--- a/ZonasEscolares/excels/PASCO-OXAPAMPA-OXAPAMPA.xlsx
+++ b/ZonasEscolares/excels/PASCO-OXAPAMPA-OXAPAMPA.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/PASCO-OXAPAMPA-OXAPAMPA.xlsx
+++ b/ZonasEscolares/excels/PASCO-OXAPAMPA-OXAPAMPA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,66 +413,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>MARIA INMACULADA</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-10.57704</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-75.40373</v>
-      </c>
-      <c r="I2" t="n">
-        <v>256</v>
-      </c>
-      <c r="J2" t="n">
-        <v>13</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-10.57704</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-75.40373</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>35005 REVERENDO PADRE BARDO BAYERLE / 35005 RVDO. PADRE BARDO BAYERLE</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-10.57607</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-75.40607</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1062</v>
-      </c>
-      <c r="J3" t="n">
-        <v>66</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-10.57607</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-75.40607</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>EMBLEMATICA DIVINA PASTORA</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-10.57723</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-75.40321</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1350</v>
-      </c>
-      <c r="J4" t="n">
-        <v>68</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-10.57723</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-75.40321</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1350</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>34205 ANA MOGAS</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-10.527376</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-75.43737299999999</v>
-      </c>
-      <c r="I5" t="n">
-        <v>381</v>
-      </c>
-      <c r="J5" t="n">
-        <v>24</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-10.527376</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-75.437373</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>34622 LIBERTADOR MARISCAL CASTILLA</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-10.57804</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-75.40295999999999</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1088</v>
-      </c>
-      <c r="J6" t="n">
-        <v>64</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-10.57804</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-75.40296</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1088</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>53 SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-10.59872</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-75.38674</v>
-      </c>
-      <c r="I7" t="n">
-        <v>518</v>
-      </c>
-      <c r="J7" t="n">
-        <v>29</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-10.59872</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-75.38674</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>518</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>SIETE DE JUNIO</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-10.172383</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-75.23002</v>
-      </c>
-      <c r="I8" t="n">
-        <v>202</v>
-      </c>
-      <c r="J8" t="n">
-        <v>12</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-10.172383</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-75.23002</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>34456</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-9.846869999999999</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-75.01638199999999</v>
-      </c>
-      <c r="I9" t="n">
-        <v>764</v>
-      </c>
-      <c r="J9" t="n">
-        <v>31</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-9.84687</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-75.016382</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>764</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>34269 AUGUSTO E. TAMAYO</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-10.437345</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-74.910847</v>
-      </c>
-      <c r="I10" t="n">
-        <v>269</v>
-      </c>
-      <c r="J10" t="n">
-        <v>16</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-10.437345</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-74.910847</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>34236 MANUEL GONZALES PRADA</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-10.83895</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-75.288304</v>
-      </c>
-      <c r="I11" t="n">
-        <v>305</v>
-      </c>
-      <c r="J11" t="n">
-        <v>25</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-10.83895</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-75.288304</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>34418 SANTA APOLONIA / SANTA APOLONIA</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-10.7403</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-75.27509999999999</v>
-      </c>
-      <c r="I12" t="n">
-        <v>333</v>
-      </c>
-      <c r="J12" t="n">
-        <v>19</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-10.7403</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-75.2751</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>34238 / 34238 ENEÑAS</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-10.7479</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-75.218</v>
-      </c>
-      <c r="I13" t="n">
-        <v>339</v>
-      </c>
-      <c r="J13" t="n">
-        <v>27</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-10.7479</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-75.218</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>34418 SANTA APOLONIA</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-10.7404</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-75.274897</v>
-      </c>
-      <c r="I14" t="n">
-        <v>247</v>
-      </c>
-      <c r="J14" t="n">
-        <v>21</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-10.7404</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-75.274897</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>JEAN PIAGET</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-10.57082</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-75.4042</v>
-      </c>
-      <c r="I15" t="n">
-        <v>315</v>
-      </c>
-      <c r="J15" t="n">
-        <v>21</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-10.57082</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-75.4042</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,22 +1377,776 @@
           <t>HAPPY KIDS</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-10.5764</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-75.4101</v>
-      </c>
-      <c r="I16" t="n">
-        <v>65</v>
-      </c>
-      <c r="J16" t="n">
-        <v>4</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-10.5764</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-75.4101</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>190301</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PASCO</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>OXAPAMPA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>OXAPAMPA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>406000</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>34207 ANTONIO BRACK EGG</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-10.584247</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-75.391781</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>190301</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PASCO</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>OXAPAMPA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>OXAPAMPA</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>406123</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ANDRES AVELINO CACERES</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-10.752909</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-75.361708</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>190301</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PASCO</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>OXAPAMPA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>OXAPAMPA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>406180</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>34206 INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-10.81713</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-75.32669</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>190301</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PASCO</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>OXAPAMPA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>OXAPAMPA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>406241</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>LOS JAZMINES</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-10.57636</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-75.39989</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>190301</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PASCO</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>OXAPAMPA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>OXAPAMPA</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>488562</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>NIÑO JESUS DE PRAGA</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-10.57302</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-75.39696</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>190301</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PASCO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>OXAPAMPA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>OXAPAMPA</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>508372</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ROMA</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-10.57182</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-75.40727</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>190301</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PASCO</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>OXAPAMPA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>OXAPAMPA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>557070</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>HUELLITAS DE INFANCIA</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-10.5854</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-75.40588</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>190301</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>PASCO</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>OXAPAMPA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>OXAPAMPA</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>744920</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>PERUANO SUIZO</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-10.56203</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-75.41295</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>190301</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PASCO</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>OXAPAMPA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>OXAPAMPA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>748193</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>TRES REYES</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-10.583993</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-75.403338</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>190301</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PASCO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>OXAPAMPA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>OXAPAMPA</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>548698</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ANTONIO BRACK EGG</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-10.576673</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-75.4013</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>190301</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>PASCO</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>OXAPAMPA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>OXAPAMPA</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>406161</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>SAGRADO CORAZON DE JESUS Y MARIA</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-10.57574</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-75.40175</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>190301</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PASCO</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>OXAPAMPA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>OXAPAMPA</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>548698</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>ANTONIO BRACK EGG</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-10.57667</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-75.4013</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/ZonasEscolares/excels/PASCO-OXAPAMPA-OXAPAMPA.xlsx
+++ b/ZonasEscolares/excels/PASCO-OXAPAMPA-OXAPAMPA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>405915</t>
+          <t>407108</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MARIA INMACULADA</t>
+          <t>SIETE DE JUNIO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-10.57704</t>
+          <t>-10.172383</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-75.40373</t>
+          <t>-75.23002</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>202</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>405977</t>
+          <t>405915</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>35005 REVERENDO PADRE BARDO BAYERLE / 35005 RVDO. PADRE BARDO BAYERLE</t>
+          <t>MARIA INMACULADA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-10.57607</t>
+          <t>-10.57704</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-75.40607</t>
+          <t>-75.40373</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>256</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>405982</t>
+          <t>408848</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>EMBLEMATICA DIVINA PASTORA</t>
+          <t>34269 AUGUSTO E. TAMAYO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-10.57723</t>
+          <t>-10.437345</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-75.40321</t>
+          <t>-74.910847</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>269</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>405996</t>
+          <t>409701</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>34205 ANA MOGAS</t>
+          <t>34418 SANTA APOLONIA / SANTA APOLONIA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-10.527376</t>
+          <t>-10.7403</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-75.437373</t>
+          <t>-75.2751</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>333</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>406156</t>
+          <t>763843</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>34622 LIBERTADOR MARISCAL CASTILLA</t>
+          <t>34418 SANTA APOLONIA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-10.57804</t>
+          <t>-10.7404</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-75.40296</t>
+          <t>-75.274897</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>247</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>406175</t>
+          <t>763895</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>53 SAN FRANCISCO DE ASIS</t>
+          <t>JEAN PIAGET</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-10.59872</t>
+          <t>-10.57082</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-75.38674</t>
+          <t>-75.4042</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>315</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>407108</t>
+          <t>405996</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SIETE DE JUNIO</t>
+          <t>34205 ANA MOGAS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-10.172383</t>
+          <t>-10.527376</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-75.23002</t>
+          <t>-75.437373</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>381</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>408725</t>
+          <t>409471</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>34456</t>
+          <t>34236 MANUEL GONZALES PRADA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-9.84687</t>
+          <t>-10.83895</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-75.016382</t>
+          <t>-75.288304</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>305</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>408848</t>
+          <t>409763</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>34269 AUGUSTO E. TAMAYO</t>
+          <t>34238 / 34238 ENEÑAS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-10.437345</t>
+          <t>-10.7479</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-74.910847</t>
+          <t>-75.218</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>339</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>409471</t>
+          <t>406175</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>34236 MANUEL GONZALES PRADA</t>
+          <t>53 SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-10.83895</t>
+          <t>-10.59872</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-75.288304</t>
+          <t>-75.38674</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>518</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>409701</t>
+          <t>408725</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>34418 SANTA APOLONIA / SANTA APOLONIA</t>
+          <t>34456</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-10.7403</t>
+          <t>-9.84687</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-75.2751</t>
+          <t>-75.016382</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>764</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>409763</t>
+          <t>906267</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>34238 / 34238 ENEÑAS</t>
+          <t>HAPPY KIDS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-10.7479</t>
+          <t>-10.5764</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-75.218</t>
+          <t>-75.4101</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>763843</t>
+          <t>406156</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>34418 SANTA APOLONIA</t>
+          <t>34622 LIBERTADOR MARISCAL CASTILLA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-10.7404</t>
+          <t>-10.57804</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-75.274897</t>
+          <t>-75.40296</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>763895</t>
+          <t>405977</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>JEAN PIAGET</t>
+          <t>35005 REVERENDO PADRE BARDO BAYERLE / 35005 RVDO. PADRE BARDO BAYERLE</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-10.57082</t>
+          <t>-10.57607</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-75.4042</t>
+          <t>-75.40607</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>66</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>906267</t>
+          <t>405982</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>HAPPY KIDS</t>
+          <t>EMBLEMATICA DIVINA PASTORA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-10.5764</t>
+          <t>-10.57723</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-75.4101</t>
+          <t>-75.40321</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>68</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>548698</t>
+          <t>406161</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ANTONIO BRACK EGG</t>
+          <t>SAGRADO CORAZON DE JESUS Y MARIA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-10.576673</t>
+          <t>-10.57574</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-75.4013</t>
+          <t>-75.40175</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>406161</t>
+          <t>548698</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SAGRADO CORAZON DE JESUS Y MARIA</t>
+          <t>ANTONIO BRACK EGG</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-10.57574</t>
+          <t>-10.57667</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-75.40175</t>
+          <t>-75.4013</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>245</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2085,68 +2085,6 @@
         </is>
       </c>
       <c r="L27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>190301</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>PASCO</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>OXAPAMPA</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>OXAPAMPA</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>548698</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>ANTONIO BRACK EGG</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>-10.57667</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>-75.4013</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/ZonasEscolares/excels/PASCO-OXAPAMPA-OXAPAMPA.xlsx
+++ b/ZonasEscolares/excels/PASCO-OXAPAMPA-OXAPAMPA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>407108</t>
+          <t>906267</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SIETE DE JUNIO</t>
+          <t>HAPPY KIDS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-10.172383</t>
+          <t>65</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-75.23002</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>-10.5764</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-75.4101</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>405915</t>
+          <t>763895</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MARIA INMACULADA</t>
+          <t>JEAN PIAGET</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-10.57704</t>
+          <t>315</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-75.40373</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>-10.57082</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-75.4042</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>408848</t>
+          <t>763843</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>34269 AUGUSTO E. TAMAYO</t>
+          <t>34418 SANTA APOLONIA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-10.437345</t>
+          <t>247</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-74.910847</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>-10.7404</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-75.274897</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>409701</t>
+          <t>748193</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>34418 SANTA APOLONIA / SANTA APOLONIA</t>
+          <t>TRES REYES</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-10.7403</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-75.2751</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>-10.583993</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-75.403338</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>763843</t>
+          <t>744920</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>34418 SANTA APOLONIA</t>
+          <t>PERUANO SUIZO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-10.7404</t>
+          <t>261</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-75.274897</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>-10.56203</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-75.41295</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>763895</t>
+          <t>557070</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JEAN PIAGET</t>
+          <t>HUELLITAS DE INFANCIA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-10.57082</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-75.4042</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>-10.5854</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-75.40588</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>405996</t>
+          <t>548698</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>34205 ANA MOGAS</t>
+          <t>ANTONIO BRACK EGG</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-10.527376</t>
+          <t>245</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-75.437373</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>-10.576673</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-75.4013</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>409471</t>
+          <t>508372</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>34236 MANUEL GONZALES PRADA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-10.83895</t>
+          <t>114</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-75.288304</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>-10.57182</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-75.40727</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>409763</t>
+          <t>488562</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>34238 / 34238 ENEÑAS</t>
+          <t>NIÑO JESUS DE PRAGA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-10.7479</t>
+          <t>77</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-75.218</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>-10.57302</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-75.39696</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>406175</t>
+          <t>409763</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>53 SAN FRANCISCO DE ASIS</t>
+          <t>34238 / 34238 ENEÑAS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-10.59872</t>
+          <t>339</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-75.38674</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>-10.7479</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-75.218</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>408725</t>
+          <t>409701</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>34456</t>
+          <t>34418 SANTA APOLONIA / SANTA APOLONIA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-9.84687</t>
+          <t>333</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-75.016382</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>-10.7403</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-75.2751</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>906267</t>
+          <t>409471</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>HAPPY KIDS</t>
+          <t>34236 MANUEL GONZALES PRADA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-10.5764</t>
+          <t>305</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-75.4101</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>-10.83895</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-75.288304</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>406156</t>
+          <t>408848</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>34622 LIBERTADOR MARISCAL CASTILLA</t>
+          <t>34269 AUGUSTO E. TAMAYO</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-10.57804</t>
+          <t>269</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-75.40296</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>-10.437345</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>-74.910847</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>405977</t>
+          <t>408725</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>35005 REVERENDO PADRE BARDO BAYERLE / 35005 RVDO. PADRE BARDO BAYERLE</t>
+          <t>34456</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-10.57607</t>
+          <t>764</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-75.40607</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>-9.84687</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>-75.016382</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>405982</t>
+          <t>407108</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>EMBLEMATICA DIVINA PASTORA</t>
+          <t>SIETE DE JUNIO</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-10.57723</t>
+          <t>202</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-75.40321</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>-10.172383</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>-75.23002</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>406000</t>
+          <t>406241</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>34207 ANTONIO BRACK EGG</t>
+          <t>LOS JAZMINES</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-10.584247</t>
+          <t>69</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-75.391781</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>-10.57636</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-75.39989</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>406123</t>
+          <t>406180</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ANDRES AVELINO CACERES</t>
+          <t>34206 INDEPENDENCIA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-10.752909</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-75.361708</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-10.81713</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-75.32669</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>406180</t>
+          <t>406175</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>34206 INDEPENDENCIA</t>
+          <t>53 SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-10.81713</t>
+          <t>518</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-75.32669</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>-10.59872</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-75.38674</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>406241</t>
+          <t>406161</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>LOS JAZMINES</t>
+          <t>SAGRADO CORAZON DE JESUS Y MARIA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-10.57636</t>
+          <t>43</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-75.39989</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>-10.57574</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-75.40175</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>488562</t>
+          <t>406156</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>NIÑO JESUS DE PRAGA</t>
+          <t>34622 LIBERTADOR MARISCAL CASTILLA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-10.57302</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-75.39696</t>
+          <t>64</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>-10.57804</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-75.40296</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>508372</t>
+          <t>406123</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>ANDRES AVELINO CACERES</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-10.57182</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-75.40727</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>-10.752909</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-75.361708</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>557070</t>
+          <t>406000</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>HUELLITAS DE INFANCIA</t>
+          <t>34207 ANTONIO BRACK EGG</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-10.5854</t>
+          <t>83</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-75.40588</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-10.584247</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-75.391781</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>744920</t>
+          <t>405996</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>PERUANO SUIZO</t>
+          <t>34205 ANA MOGAS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-10.56203</t>
+          <t>381</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-75.41295</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>-10.527376</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-75.437373</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>748193</t>
+          <t>405982</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>TRES REYES</t>
+          <t>EMBLEMATICA DIVINA PASTORA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-10.583993</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-75.403338</t>
+          <t>68</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>-10.575324</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-75.40395</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>406161</t>
+          <t>405977</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SAGRADO CORAZON DE JESUS Y MARIA</t>
+          <t>35005 REVERENDO PADRE BARDO BAYERLE / 35005 RVDO. PADRE BARDO BAYERLE</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-10.57574</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-75.40175</t>
+          <t>66</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-10.57607</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-75.40607</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>548698</t>
+          <t>405915</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ANTONIO BRACK EGG</t>
+          <t>MARIA INMACULADA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-10.57667</t>
+          <t>256</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-75.4013</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>-10.57704</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-75.40373</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">

--- a/ZonasEscolares/excels/PASCO-OXAPAMPA-OXAPAMPA.xlsx
+++ b/ZonasEscolares/excels/PASCO-OXAPAMPA-OXAPAMPA.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
